--- a/data/incremental/incremental_02_vitacura_manual.xlsx
+++ b/data/incremental/incremental_02_vitacura_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG25"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -460,7 +460,7 @@
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Piegari Chile</t>
+          <t>Ofelia Gastrobar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -643,42 +643,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Av. Nueva Costanera 4092, 7630191 Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 3201, 7630578 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9 3453 7621</t>
+          <t>(2) 2944 7800</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>http://www.piegari.cl/</t>
+          <t>https://www.ofeliagastrobar.com/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restaurante italiano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Piegari+Chile/data=!4m7!3m6!1s0x9662cfe62edf92cf:0xe56813440fe5a463!8m2!3d-33.3954005!4d-70.5975267!16s%2Fg%2F11dyrb51w7!19sChIJz5LfLubPYpYRY6TlD0QTaOU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Ofelia+Gastrobar/data=!4m7!3m6!1s0x9662cf94400bd1d1:0xab1af5b17f27cd4e!8m2!3d-33.4074623!4d-70.5985484!16s%2Fg%2F11ryt4r0yc!19sChIJ0dELQJTPYpYRTs0nf7H1Gqs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-33.3954005</t>
+          <t>-33.4074623</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-70.5975267</t>
+          <t>-70.5985484</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -736,52 +736,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>APPA Restaurante</t>
+          <t>CAOBA BAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>834</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Av Vitacura 7501, 7650296 Vitacura, Región Metropolitana</t>
+          <t>Alonso de Córdova 4156, 7630448 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9 7430 8508</t>
+          <t>9 5855 6596</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://toteat.app/r/cl/APPA---VITACURA/9255</t>
+          <t>https://caobabar.cl/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar restaurante</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/APPA+Restaurante/@-33.386285,-70.5618881,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c9004da0f611:0x507e760a4ead2bf0!8m2!3d-33.386285!4d-70.5618881!16s%2Fg%2F11w1k7qgxk?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/CAOBA+BAR/data=!4m7!3m6!1s0x9662cfec8b5a7381:0x776af53046b0faf0!8m2!3d-33.4026497!4d-70.5901323!16s%2Fg%2F11tcwmj81r!19sChIJgXNai-zPYpYR8PqwRjD1anc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-33.386285</t>
+          <t>-33.4026497</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-70.5618881</t>
+          <t>-70.5901323</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,48 +839,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mestizo</t>
+          <t>Piegari Chile</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Av. Bicentenario 4050, Santiago, Vitacura, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Av. Nueva Costanera 4092, 7630191 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9 3453 7621</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://mestizorestaurant.cl/</t>
+          <t>http://www.piegari.cl/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Restaurante de alta cocina</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mestizo/data=!4m7!3m6!1s0x9662cf4bb499917f:0xfd06a131a5f08a6d!8m2!3d-33.3942718!4d-70.5999298!16s%2Fg%2F1tmqm_0s!19sChIJf5GZtEvPYpYRbYrwpTGhBv0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Piegari+Chile/data=!4m7!3m6!1s0x9662cfe62edf92cf:0xe56813440fe5a463!8m2!3d-33.3954005!4d-70.5975267!16s%2Fg%2F11dyrb51w7!19sChIJz5LfLubPYpYRY6TlD0QTaOU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-33.3942718</t>
+          <t>-33.3954005</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-70.5999298</t>
+          <t>-70.5975267</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -933,61 +937,53 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tanaka Vitacura</t>
+          <t>Mestizo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 4248, 7630504 Santiago, Vitacura, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>9 7443 4824</t>
-        </is>
-      </c>
+          <t>Av. Bicentenario 4050, Santiago, Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>http://www.tanaka.cl/vitacura</t>
+          <t>https://mestizorestaurant.cl/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante de alta cocina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tanaka+Vitacura/data=!4m7!3m6!1s0x9662cf3719587b89:0x472600fb6eb00235!8m2!3d-33.4030473!4d-70.5886892!16s%2Fg%2F11ckw294gm!19sChIJiXtYGTfPYpYRNQKwbvsAJkc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Mestizo/data=!4m7!3m6!1s0x9662cf4bb499917f:0xfd06a131a5f08a6d!8m2!3d-33.3942718!4d-70.5999298!16s%2Fg%2F1tmqm_0s!19sChIJf5GZtEvPYpYRbYrwpTGhBv0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.4030473</t>
+          <t>-33.3942718</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-70.5886892</t>
+          <t>-70.5999298</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1012,12 +1008,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1040,37 +1036,41 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>La Mar by Gaston Acurio</t>
+          <t>Casa Sanz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Av. Nueva Costanera 4076, 7630191 Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 4873, 7630000 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(2) 2617 0848</t>
+          <t>9 9165 1370</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.lamarcebicheria.com/santiago-de-chile/</t>
+          <t>https://hotelbidasoa.cl/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Mar+by+Gaston+Acurio/data=!4m7!3m6!1s0x9662cf3561295821:0x184796e8fe9b36c0!8m2!3d-33.395535!4d-70.59766!16s%2Fg%2F11bw3d5xb0!19sChIJIVgpYTXPYpYRwDab_uiWRxg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Casa+Sanz/data=!4m7!3m6!1s0x9662cfaa42f67979:0x78939ae5f730c248!8m2!3d-33.3982681!4d-70.5851944!16s%2Fg%2F11sjxnlkxg!19sChIJeXn2QqrPYpYRSMIw9-Wak3g?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.395535</t>
+          <t>-33.3982681</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-70.59766</t>
+          <t>-70.5851944</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Capogrossi</t>
+          <t>Tanaka Vitacura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1158,42 +1158,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 4225, 7630524 Vitacura, Región Metropolitana</t>
+          <t>Alonso de Córdova 4248, 7630504 Santiago, Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9 4469 3223</t>
+          <t>9 7443 4824</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://capogrossi.cl/</t>
+          <t>http://www.tanaka.cl/vitacura</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restaurante italiano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Capogrossi/@-33.4034028,-70.5893016,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfac4ffe31d1:0x7000c380cbd5efe5!8m2!3d-33.4034028!4d-70.5893016!16s%2Fg%2F11s51d17m6?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Tanaka+Vitacura/data=!4m7!3m6!1s0x9662cf3719587b89:0x472600fb6eb00235!8m2!3d-33.4030473!4d-70.5886892!16s%2Fg%2F11ckw294gm!19sChIJiXtYGTfPYpYRNQKwbvsAJkc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.4034028</t>
+          <t>-33.4030473</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-70.5893016</t>
+          <t>-70.5886892</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1251,32 +1251,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rubaiyat Chile</t>
+          <t>La Mar by Gaston Acurio</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Av. Nueva Costanera 4031, 7630244 Vitacura, Región Metropolitana</t>
+          <t>Av. Nueva Costanera 4076, 7630191 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(2) 2617 9800</t>
+          <t>(2) 2617 0848</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://gruporubaiyat.com/es/</t>
+          <t>https://www.lamarcebicheria.com/santiago-de-chile/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Rubaiyat+Chile/@-33.3963918,-70.5970912,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf357c0dc795:0xdfa8171effe5e3bd!8m2!3d-33.3963918!4d-70.5970912!16s%2Fg%2F11cm0584gn?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Mar+by+Gaston+Acurio/data=!4m7!3m6!1s0x9662cf3561295821:0x184796e8fe9b36c0!8m2!3d-33.395535!4d-70.59766!16s%2Fg%2F11bw3d5xb0!19sChIJIVgpYTXPYpYRwDab_uiWRxg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.3963918</t>
+          <t>-33.395535</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-70.5970912</t>
+          <t>-70.59766</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1354,52 +1354,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kechua Vitacura</t>
+          <t>Capogrossi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Costanera Sur S.J.E. de Balaguer 6400, LUG 2-A, 7630000 Vitacura, Región Metropolitana</t>
+          <t>Alonso de Córdova 4225, 7630524 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(2) 2427 9686</t>
+          <t>9 4469 3223</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://kechuarestaurantes.cl/borderio/</t>
+          <t>https://capogrossi.cl/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kechua+Vitacura/data=!4m7!3m6!1s0x9662c91a55258adf:0x8b4d8fd1119ebaae!8m2!3d-33.3817562!4d-70.57943!16s%2Fg%2F11sj5dh_jm!19sChIJ34olVRrJYpYRrrqeEdGPTYs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Capogrossi/data=!4m7!3m6!1s0x9662cfac4ffe31d1:0x7000c380cbd5efe5!8m2!3d-33.4034028!4d-70.5893016!16s%2Fg%2F11s51d17m6!19sChIJ0TH-T6zPYpYR5e_Vy4DDAHA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.3817562</t>
+          <t>-33.4034028</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-70.57943</t>
+          <t>-70.5893016</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1457,52 +1457,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arca Bar</t>
+          <t>APPA Restaurante</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Av. Nueva Costanera 3986, 7630000 Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 7501, 7650296 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9 6839 9315</t>
+          <t>9 7430 8508</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.grupoarca.cl/</t>
+          <t>https://toteat.app/r/cl/APPA---VITACURA/9255</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arca+Bar/data=!4m7!3m6!1s0x9662cfe6bdc049f1:0xae691c9d8f796c3d!8m2!3d-33.3972025!4d-70.597931!16s%2Fg%2F11q1n_nb_5!19sChIJ8UnAvebPYpYRPWx5j50caa4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/APPA+Restaurante/data=!4m7!3m6!1s0x9662c9004da0f611:0x507e760a4ead2bf0!8m2!3d-33.386285!4d-70.5618881!16s%2Fg%2F11w1k7qgxk!19sChIJEfagTQDJYpYR8CutTgp2flA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.3972025</t>
+          <t>-33.386285</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-70.597931</t>
+          <t>-70.5618881</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Panchita</t>
+          <t>El Toro Vitacura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1570,38 +1570,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Av. Nueva Costanera 3979, 7630268 Vitacura, Región Metropolitana</t>
+          <t>Alonso de Córdova 3788, piso -1, 7630000 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9 9609 4839</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>9 3201 9661</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>http://www.eltoro.cl/</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Panchita/data=!4m7!3m6!1s0x9662cfe8f6df9f3d:0x3697a17c33501e74!8m2!3d-33.397429!4d-70.59735!16s%2Fg%2F11h7cwv3y7!19sChIJPZ_f9ujPYpYRdB5QM3yhlzY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/El+Toro+Vitacura/data=!4m7!3m6!1s0x9662cf89a33b0f49:0x1b187e22a345a7e0!8m2!3d-33.4018737!4d-70.5929112!16s%2Fg%2F11sw_ws1rr!19sChIJSQ87o4nPYpYR4KdFoyJ-GBs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.397429</t>
+          <t>-33.4018737</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-70.59735</t>
+          <t>-70.5929112</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1626,12 +1630,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1659,7 +1663,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ofelia Gastrobar</t>
+          <t>Arca Bar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1669,42 +1673,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Av Vitacura 3201, 7630578 Vitacura, Región Metropolitana</t>
+          <t>Av. Nueva Costanera 3986, 7630000 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(2) 2944 7800</t>
+          <t>9 6839 9315</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ofeliagastrobar.com/</t>
+          <t>https://www.grupoarca.cl/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ofelia+Gastrobar/data=!4m7!3m6!1s0x9662cf94400bd1d1:0xab1af5b17f27cd4e!8m2!3d-33.4074623!4d-70.5985484!16s%2Fg%2F11ryt4r0yc!19sChIJ0dELQJTPYpYRTs0nf7H1Gqs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Arca+Bar/data=!4m7!3m6!1s0x9662cfe6bdc049f1:0xae691c9d8f796c3d!8m2!3d-33.3972025!4d-70.597931!16s%2Fg%2F11q1n_nb_5!19sChIJ8UnAvebPYpYRPWx5j50caa4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.4074623</t>
+          <t>-33.3972025</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-70.5985484</t>
+          <t>-70.597931</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1729,7 +1733,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1739,7 +1743,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1762,52 +1766,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rishtedar Vitacura</t>
+          <t>Restaurant Miraolas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Av Vitacura 5461, 7630598 Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 4171, 7630358 Santiago, Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9 8888 3581</t>
+          <t>9 8385 0206</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>http://www.rishtedar.cl/</t>
+          <t>http://www.miraolas.cl/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Restaurante indio</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Rishtedar+Vitacura/@-33.3950354,-70.5790121,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf2b93ed4dff:0x907266614eb68b68!8m2!3d-33.3950354!4d-70.5790121!16s%2Fg%2F11cmsvbxwj?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Miraolas/data=!4m7!3m6!1s0x9662cf316d7aaf55:0xfb7f125473d331be!8m2!3d-33.3999035!4d-70.5900577!16s%2Fg%2F1tfcdcry!19sChIJVa96bTHPYpYRvjHTc1QSf_s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.3950354</t>
+          <t>-33.3999035</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-70.5790121</t>
+          <t>-70.5900577</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1832,7 +1836,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1865,7 +1869,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Cabrera Chile</t>
+          <t>Rubaiyat Chile</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1875,42 +1879,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 4263, 7630530 Vitacura, Región Metropolitana</t>
+          <t>Av. Nueva Costanera 4031, 7630244 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9 3236 1687</t>
+          <t>(2) 2617 9800</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>http://www.lacabrerachile.cl/</t>
+          <t>https://gruporubaiyat.com/es/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Restaurante especializado en filetes</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Cabrera+Chile/@-33.4035466,-70.5885212,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf307ee64289:0x23ce2fd63de5a73b!8m2!3d-33.4035466!4d-70.5885212!16s%2Fg%2F11f5h206bw?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Rubaiyat+Chile/data=!4m7!3m6!1s0x9662cf357c0dc795:0xdfa8171effe5e3bd!8m2!3d-33.3963918!4d-70.5970912!16s%2Fg%2F11cm0584gn!19sChIJlccNfDXPYpYRvePl_x4XqN8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.4035466</t>
+          <t>-33.3963918</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-70.5885212</t>
+          <t>-70.5970912</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1935,7 +1939,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1968,52 +1972,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAOKI</t>
+          <t>Kechua Vitacura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>495</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Av Vitacura 3875, 7630358 Vitacura, Región Metropolitana</t>
+          <t>Costanera Sur S.J.E. de Balaguer 6400, LUG 2-A, 7630000 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(2) 2656 6281</t>
+          <t>(2) 2427 9686</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>http://www.naoki.cl/</t>
+          <t>https://kechuarestaurantes.cl/borderio/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Restaurante japonés</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/NAOKI/data=!4m7!3m6!1s0x9662cf36cf07b1d1:0x85749e2f812b2850!8m2!3d-33.4005682!4d-70.5922715!16s%2Fg%2F11bw82cvts!19sChIJ0bEHzzbPYpYRUCgrgS-edIU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Kechua+Vitacura/data=!4m7!3m6!1s0x9662c91a55258adf:0x8b4d8fd1119ebaae!8m2!3d-33.3817562!4d-70.57943!16s%2Fg%2F11sj5dh_jm!19sChIJ34olVRrJYpYRrrqeEdGPTYs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.4005682</t>
+          <t>-33.3817562</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-70.5922715</t>
+          <t>-70.57943</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2038,7 +2042,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2071,7 +2075,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bar Santiago Vitacura</t>
+          <t>Rishtedar Vitacura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2081,42 +2085,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Av Vitacura 7120, 7640560 Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 5461, 7630598 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9 7996 4119</t>
+          <t>9 8888 3581</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://barsantiago.cl/</t>
+          <t>http://www.rishtedar.cl/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bar restaurante</t>
+          <t>Restaurante indio</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bar+Santiago+Vitacura/@-33.3867402,-70.5649557,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c9465439ed5d:0x1ee5cf0006f07af3!8m2!3d-33.3867402!4d-70.5649557!16s%2Fg%2F11tjf5xr59?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Rishtedar+Vitacura/data=!4m7!3m6!1s0x9662cf2b93ed4dff:0x907266614eb68b68!8m2!3d-33.3950354!4d-70.5790121!16s%2Fg%2F11cmsvbxwj!19sChIJ_03tkyvPYpYRaIu2TmFmcpA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.3867402</t>
+          <t>-33.3950354</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-70.5649557</t>
+          <t>-70.5790121</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2141,7 +2145,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2174,30 +2178,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Restaurant Bidasoa</t>
+          <t>Demencia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Av Vitacura 4873, Santiago, Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 3520, 7630523 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9 9165 1370</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>9 3861 1684</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/demenciastgo/</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -2205,17 +2213,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Bidasoa/@-33.398398,-70.5852397,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf2e10900001:0xd59acb69f36fa720!8m2!3d-33.398398!4d-70.5852397!16s%2Fg%2F11ggs33nwx?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Demencia/data=!4m7!3m6!1s0x9662cfb61d16452b:0x6108ad9a3153fe62!8m2!3d-33.4039236!4d-70.5964995!16s%2Fg%2F11rcscbqmr!19sChIJK0UWHbbPYpYRYv5TMZqtCGE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.398398</t>
+          <t>-33.4039236</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-70.5852397</t>
+          <t>-70.5964995</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2240,12 +2248,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2273,48 +2281,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Casa las Cujas</t>
+          <t>Bar Santiago Vitacura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>866</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 2467, 7630418 Vitacura, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Av Vitacura 7120, 7640560 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9 7996 4119</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>http://www.lascujas.com/</t>
+          <t>https://barsantiago.cl/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar restaurante</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casa+las+Cujas/data=!4m7!3m6!1s0x9662cf479569afc7:0xb190f10166d4f431!8m2!3d-33.4012398!4d-70.5955414!16s%2Fg%2F11g81d0nxs!19sChIJx69plUfPYpYRMfTUZgHxkLE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Bar+Santiago+Vitacura/data=!4m7!3m6!1s0x9662c9465439ed5d:0x1ee5cf0006f07af3!8m2!3d-33.3867402!4d-70.5649557!16s%2Fg%2F11tjf5xr59!19sChIJXe05VEbJYpYR83rwBgDP5R4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.4012398</t>
+          <t>-33.3867402</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-70.5955414</t>
+          <t>-70.5649557</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2339,12 +2351,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2367,61 +2379,53 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Casa Vieja</t>
+          <t>Panchita</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Av Vitacura 8411, 7650223 Vitacura, Santiago, Región Metropolitana</t>
+          <t>Av. Nueva Costanera 3979, 7630268 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(2) 2202 0355</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>http://www.lacasavieja.cl/</t>
-        </is>
-      </c>
+          <t>9 9609 4839</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Casa+Vieja/@-33.384984,-70.55377,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c934f17b4247:0x7b277f0f558d4d2c!8m2!3d-33.384984!4d-70.55377!16s%2Fg%2F11bvvzwnkt?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Panchita/data=!4m7!3m6!1s0x9662cfe8f6df9f3d:0x3697a17c33501e74!8m2!3d-33.397429!4d-70.59735!16s%2Fg%2F11h7cwv3y7!19sChIJPZ_f9ujPYpYRdB5QM3yhlzY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.384984</t>
+          <t>-33.397429</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-70.55377</t>
+          <t>-70.59735</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2479,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>The Crust</t>
+          <t>NAOKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2489,42 +2493,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Av Vitacura 5321, 7630185 Vitacura, Región Metropolitana</t>
+          <t>Av Vitacura 3875, 7630358 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9 4213 3773</t>
+          <t>(2) 2656 6281</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.thecrust.cl/</t>
+          <t>http://www.naoki.cl/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hamburguesería</t>
+          <t>Restaurante japonés</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/The+Crust/data=!4m7!3m6!1s0x9662cf771d402e65:0x2056fe74e7216ecf!8m2!3d-33.3965954!4d-70.5813768!16s%2Fg%2F11v0grc11k!19sChIJZS5AHXfPYpYRz24h53T-ViA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/NAOKI/data=!4m7!3m6!1s0x9662cf36cf07b1d1:0x85749e2f812b2850!8m2!3d-33.4005682!4d-70.5922715!16s%2Fg%2F11bw82cvts!19sChIJ0bEHzzbPYpYRUCgrgS-edIU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.3965954</t>
+          <t>-33.4005682</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-70.5813768</t>
+          <t>-70.5922715</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2559,7 +2563,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2577,16 +2581,12 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Revisar: parece hamburgueseria</t>
-        </is>
-      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>La Dicha Restaurant</t>
+          <t>La Mesa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2596,42 +2596,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>513</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 4355, 7560801 Vitacura, Región Metropolitana</t>
+          <t>Alonso de Córdova 2767, 7630000 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9 7478 8996</t>
+          <t>9 9072 2461</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>http://www.ladicha.cl/</t>
+          <t>http://www.restaurantlamesa.com/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Restaurante de alta cocina</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Dicha+Restaurant/data=!4m7!3m6!1s0x9662cf8c16450497:0x66b3dc98ab485629!8m2!3d-33.4039613!4d-70.5874015!16s%2Fg%2F11h512d0ch!19sChIJlwRFFozPYpYRKVZIq5jcs2Y?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Mesa/data=!4m7!3m6!1s0x9662cf89e863dc69:0xd8e5666a83d5ddcd!8m2!3d-33.4009536!4d-70.5971205!16s%2Fg%2F11hzjhshtx!19sChIJadxj6InPYpYRzd3Vg2pm5dg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.4039613</t>
+          <t>-33.4009536</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-70.5874015</t>
+          <t>-70.5971205</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2689,52 +2689,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Santa Brasa Alonso de Córdova</t>
+          <t>Saffron Chile</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>459</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 4260, 7630504 Vitacura, Región Metropolitana</t>
+          <t>Av. Nueva Costanera 3666, L-2, 8320000 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9 9064 5249</t>
+          <t>(2) 2502 2020</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.santabrasa.cl/</t>
+          <t>https://www.saffronchile.cl/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante indio</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Santa+Brasa+Alonso+de+C%C3%B3rdova/data=!4m7!3m6!1s0x9662cf307ec41f55:0x1d70c27a25d90a09!8m2!3d-33.4031334!4d-70.5885467!16s%2Fg%2F1vh_9l3p!19sChIJVR_EfjDPYpYRCQrZJXrCcB0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Saffron+Chile/data=!4m7!3m6!1s0x9662cf49d3b039e1:0x9fb450f388645d4!8m2!3d-33.4029969!4d-70.598644!16s%2Fg%2F1q62d26j1!19sChIJ4Tmw00nPYpYR1EWGOA9F-wk?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.4031334</t>
+          <t>-33.4029969</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-70.5885467</t>
+          <t>-70.598644</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2792,52 +2792,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Starnberg</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 2359, 7630415 Vitacura, Región Metropolitana</t>
+          <t>Av. Nueva Costanera 3736, 7630428 Vitacura, Región Metropolitana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(2) 2953 5100</t>
+          <t>9 8879 0342</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>http://www.starnberg.cl/</t>
+          <t>https://www.osakanikkei.com/es/local/santiago</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Restaurante alemán</t>
+          <t>Restaurante de sushi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Starnberg/data=!4m7!3m6!1s0x9662cf3701f09d87:0xe79b074bb9003930!8m2!3d-33.401477!4d-70.594762!16s%2Fg%2F1tnl2lww!19sChIJh53wATfPYpYRMDkAuUsHm-c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Osaka/data=!4m7!3m6!1s0x9662cf4076d010a1:0xde17a5a2f4e9a102!8m2!3d-33.401405!4d-70.598515!16s%2Fg%2F11byxfkkrn!19sChIJoRDQdkDPYpYRAqHp9KKlF94?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.401477</t>
+          <t>-33.401405</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-70.594762</t>
+          <t>-70.598515</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dipsy's Backyard</t>
+          <t>Aquí Está Coco</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2905,38 +2905,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>483</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Av. Nueva Costanera 3122, 7550000 Vitacura, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Av. Nueva Costanera 3960, 7630267 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9 6341 1510</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>http://www.dipsys.cl/</t>
+          <t>http://aquiestacoco.cl/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Restaurante americano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Dipsy%27s+Backyard/data=!4m7!3m6!1s0x9662cf32bae7c8db:0x18278e6422944fd9!8m2!3d-33.4062405!4d-70.599158!16s%2Fg%2F11swzwgnvh!19sChIJ28jnujLPYpYR2U-UImSOJxg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Aqu%C3%AD+Est%C3%A1+Coco/data=!4m7!3m6!1s0x9662cf0fd17c1585:0x61b13a99d84ed43!8m2!3d-33.3977481!4d-70.5980472!16s%2Fg%2F11s0k225gg!19sChIJhRV80Q_PYpYRQ-2EnakTGwY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.4062405</t>
+          <t>-33.3977481</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.599158</t>
+          <t>-70.5980472</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2961,12 +2965,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2989,11 +2993,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/DonDoh+Santiago/@-33.3976336,-70.597372,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf8144be45f1:0x68dab0b63d2b0697!8m2!3d-33.3976336!4d-70.597372!16s%2Fg%2F11qpvd13z_?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/DonDoh+Santiago/data=!4m7!3m6!1s0x9662cf8144be45f1:0x68dab0b63d2b0697!8m2!3d-33.3976336!4d-70.597372!16s%2Fg%2F11qpvd13z_!19sChIJ8UW-RIHPYpYRlwYrPbaw2mg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3098,8 +3098,622 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>La Cocina de Javier - Restaurant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Av Vitacura 7482, 7640534 Santiago, Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(2) 2495 7750</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>http://lacocinadejavier.cl/</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Restaurante de cocina española</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/La+Cocina+de+Javier+-+Restaurant/data=!4m7!3m6!1s0x9662cf3a9e7bc34f:0xa8ae31b5dae77065!8m2!3d-33.3856949!4d-70.5611474!16s%2Fg%2F1tdvqyty!19sChIJT8N7njrPYpYRZXDn2rUxrqg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-33.3856949</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-70.5611474</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Starnberg</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Alonso de Córdova 2359, 7630415 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(2) 2953 5100</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>http://www.starnberg.cl/</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Restaurante alemán</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Starnberg/data=!4m7!3m6!1s0x9662cf3701f09d87:0xe79b074bb9003930!8m2!3d-33.401477!4d-70.594762!16s%2Fg%2F1tnl2lww!19sChIJh53wATfPYpYRMDkAuUsHm-c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-33.401477</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-70.594762</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Barceloneta</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Av Vitacura 3391, 7630564 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://barcelonetasantiago.com/</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barceloneta/data=!4m7!3m6!1s0x9662cfa76461b4fd:0x58bb79a751db2280!8m2!3d-33.4053922!4d-70.5972991!16s%2Fg%2F11l6mbcws2!19sChIJ_bRhZKfPYpYRgCLbUad5u1g?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-33.4053922</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-70.5972991</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Casa las Cujas</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Alonso de Córdova 2467, 7630418 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>http://www.lascujas.com/</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Casa+las+Cujas/data=!4m7!3m6!1s0x9662cf479569afc7:0xb190f10166d4f431!8m2!3d-33.4012398!4d-70.5955414!16s%2Fg%2F11g81d0nxs!19sChIJx69plUfPYpYRMfTUZgHxkLE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.4012398</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-70.5955414</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cala El Mañío</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Av Vitacura 3859, 7630358 Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9 9820 9480</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://calaelmanio.cl/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Cala+El+Ma%C3%B1%C3%ADo/data=!4m7!3m6!1s0x9662cf81bd29e2b9:0x551b182822f195e4!8m2!3d-33.4007017!4d-70.5923728!16s%2Fg%2F11h7ptkqdv!19sChIJueIpvYHPYpYR5JXxIigYG1U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-33.4007017</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-70.5923728</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Restaurant Bidasoa</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Av Vitacura 4873, Santiago, Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>9 9165 1370</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Restaurant+Bidasoa/data=!4m7!3m6!1s0x9662cf2e10900001:0xd59acb69f36fa720!8m2!3d-33.398398!4d-70.5852397!16s%2Fg%2F11ggs33nwx!19sChIJAQCQEC7PYpYRIKdv82nLmtU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-33.398398</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-70.5852397</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG25"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>